--- a/artfynd/A 34184-2022 artfynd.xlsx
+++ b/artfynd/A 34184-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34184-2022 artfynd.xlsx
+++ b/artfynd/A 34184-2022 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>104157989</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>865707.8430650271</v>
+        <v>865707</v>
       </c>
       <c r="R2" t="n">
-        <v>7348966.305428875</v>
+        <v>7348966</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
